--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119964789</v>
+        <v>119966008</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,42 +1040,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R5" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119966008</v>
+        <v>119964789</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,54 +1164,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R6" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119964771</v>
+        <v>119966008</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -956,14 +956,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R4" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119966008</v>
+        <v>119964771</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1080,14 +1080,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R5" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1155,7 +1155,7 @@
         <v>119964789</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119966008</v>
+        <v>119964789</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,54 +916,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R4" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119964771</v>
+        <v>119966008</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1063,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1080,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R5" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1152,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119964789</v>
+        <v>119964771</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,30 +1152,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119966008</v>
+        <v>119964771</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R5" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119964771</v>
+        <v>119966008</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1192,14 +1192,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R6" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119964789</v>
+        <v>119964771</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,30 +916,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1016,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119964771</v>
+        <v>119964789</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,42 +1040,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119964789</v>
+        <v>119966008</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,42 +1040,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R5" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119966008</v>
+        <v>119964789</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,54 +1164,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R6" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 28412-2024 artfynd.xlsx
+++ b/artfynd/A 28412-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119964771</v>
+        <v>119964789</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,42 +916,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1028,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119966008</v>
+        <v>119964771</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1063,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1080,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrikhult SO 770 m, Ög</t>
+          <t>Skrikhult SO-S 730 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559071</v>
+        <v>559037</v>
       </c>
       <c r="R5" t="n">
-        <v>6503089</v>
+        <v>6503120</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1152,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119964789</v>
+        <v>119966008</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,42 +1152,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrikhult SO-S 730 m, Ög</t>
+          <t>Skrikhult SO 770 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559037</v>
+        <v>559071</v>
       </c>
       <c r="R6" t="n">
-        <v>6503120</v>
+        <v>6503089</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
